--- a/data/trans_dic/P68-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P68-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,92; 34,79</t>
+          <t>25,05; 34,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,48; 39,02</t>
+          <t>24,85; 38,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,95; 48,21</t>
+          <t>31,69; 48,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,33; 30,88</t>
+          <t>15,54; 30,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,9; 33,43</t>
+          <t>18,42; 33,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,87; 35,02</t>
+          <t>19,61; 35,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,27; 35,06</t>
+          <t>15,64; 37,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,71; 46,03</t>
+          <t>22,31; 48,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,08; 32,41</t>
+          <t>24,01; 32,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,19; 35,19</t>
+          <t>25,27; 35,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,67; 41,94</t>
+          <t>28,33; 41,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,62; 32,88</t>
+          <t>19,45; 32,3</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,03; 28,51</t>
+          <t>22,94; 28,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,81; 27,73</t>
+          <t>21,89; 27,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,08; 28,1</t>
+          <t>22,17; 27,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 22,29</t>
+          <t>10,4; 22,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,14; 23,72</t>
+          <t>17,15; 23,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,12; 26,69</t>
+          <t>19,74; 26,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,29; 22,55</t>
+          <t>15,84; 22,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,28; 33,35</t>
+          <t>19,88; 34,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,99; 26,26</t>
+          <t>22,05; 26,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,77; 26,47</t>
+          <t>21,76; 26,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,42; 24,67</t>
+          <t>20,31; 24,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 25,19</t>
+          <t>14,76; 24,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 22,55</t>
+          <t>14,73; 22,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,1; 19,66</t>
+          <t>10,82; 19,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 23,44</t>
+          <t>14,2; 23,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 19,86</t>
+          <t>12,43; 20,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,31; 26,65</t>
+          <t>17,67; 27,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 26,2</t>
+          <t>14,56; 25,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,35; 29,77</t>
+          <t>19,71; 29,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 24,57</t>
+          <t>17,07; 24,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 23,1</t>
+          <t>16,84; 23,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,78; 20,3</t>
+          <t>13,55; 20,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,94; 24,51</t>
+          <t>17,56; 24,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,74; 20,91</t>
+          <t>15,8; 20,85</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,82; 26,77</t>
+          <t>22,95; 26,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,12; 25,76</t>
+          <t>21,13; 25,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,45; 27,08</t>
+          <t>22,49; 27,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,39; 20,64</t>
+          <t>11,4; 20,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,41</t>
+          <t>19,23; 24,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,09; 25,78</t>
+          <t>20,19; 26,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,45; 23,65</t>
+          <t>18,55; 23,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,03; 30,06</t>
+          <t>20,81; 30,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,11; 25,31</t>
+          <t>22,16; 25,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,43; 24,73</t>
+          <t>21,61; 25,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,55; 24,96</t>
+          <t>21,61; 25,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,48; 23,21</t>
+          <t>15,64; 23,38</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93459; 130473</t>
+          <t>93924; 130014</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46888; 71808</t>
+          <t>45725; 71693</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43319; 67477</t>
+          <t>44353; 68077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20247; 40794</t>
+          <t>20530; 39937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28534; 50482</t>
+          <t>27814; 51069</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27819; 49016</t>
+          <t>27454; 49099</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11562; 24904</t>
+          <t>11107; 26400</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17499; 37104</t>
+          <t>17980; 38843</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126679; 170500</t>
+          <t>126307; 169820</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81620; 114016</t>
+          <t>81889; 114424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60507; 88501</t>
+          <t>59771; 87669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41734; 69932</t>
+          <t>41372; 68713</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>256348; 317390</t>
+          <t>255359; 316321</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>199464; 253625</t>
+          <t>200203; 254018</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>203217; 258605</t>
+          <t>204028; 257110</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124391; 302963</t>
+          <t>141429; 303579</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>99273; 137367</t>
+          <t>99337; 136723</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>109534; 152898</t>
+          <t>113078; 152235</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>106142; 146971</t>
+          <t>103232; 145667</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>188260; 309597</t>
+          <t>184549; 316947</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>372115; 444361</t>
+          <t>373136; 442629</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323814; 393650</t>
+          <t>323724; 392025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>320981; 387906</t>
+          <t>319342; 389475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>345202; 576223</t>
+          <t>337741; 566409</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>58813; 91406</t>
+          <t>59683; 90633</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35102; 62165</t>
+          <t>34215; 61015</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49580; 81250</t>
+          <t>49208; 81458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52685; 88487</t>
+          <t>55365; 89487</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50428; 77642</t>
+          <t>51497; 78943</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35048; 61551</t>
+          <t>34207; 60274</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59098; 90901</t>
+          <t>60180; 90255</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76477; 107190</t>
+          <t>74494; 105518</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118198; 160952</t>
+          <t>117316; 160206</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75940; 111890</t>
+          <t>74707; 111718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116997; 159817</t>
+          <t>114460; 158635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>138766; 184340</t>
+          <t>139340; 183807</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>432161; 506905</t>
+          <t>434510; 510003</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>298788; 364414</t>
+          <t>298910; 363615</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>315904; 380945</t>
+          <t>316405; 382777</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>220703; 399871</t>
+          <t>220888; 404307</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>195809; 249326</t>
+          <t>196389; 247541</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>190408; 244374</t>
+          <t>191311; 247103</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>189712; 243154</t>
+          <t>190735; 241835</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>303903; 434415</t>
+          <t>300676; 434694</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>644460; 737682</t>
+          <t>646055; 740870</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>506362; 584174</t>
+          <t>510530; 591191</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>524749; 607799</t>
+          <t>526318; 609260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>557443; 785016</t>
+          <t>529111; 790612</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P68-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P68-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,05; 34,67</t>
+          <t>25,18; 34,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,85; 38,96</t>
+          <t>24,97; 38,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,69; 48,64</t>
+          <t>31,32; 48,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 30,23</t>
+          <t>16,03; 29,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,42; 33,82</t>
+          <t>18,61; 32,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,61; 35,08</t>
+          <t>20,57; 35,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,64; 37,16</t>
+          <t>16,73; 37,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,31; 48,19</t>
+          <t>19,61; 35,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,01; 32,29</t>
+          <t>24,36; 32,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,27; 35,32</t>
+          <t>24,74; 35,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 41,55</t>
+          <t>28,14; 41,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,45; 32,3</t>
+          <t>19,09; 30,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,94; 28,42</t>
+          <t>23,06; 28,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,89; 27,78</t>
+          <t>21,8; 27,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,17; 27,94</t>
+          <t>21,97; 27,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,4; 22,33</t>
+          <t>19,0; 23,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,15; 23,61</t>
+          <t>17,25; 23,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,74; 26,57</t>
+          <t>19,15; 26,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 22,35</t>
+          <t>16,36; 22,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,88; 34,14</t>
+          <t>21,27; 26,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,05; 26,16</t>
+          <t>22,04; 26,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,76; 26,36</t>
+          <t>21,75; 26,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,31; 24,77</t>
+          <t>20,68; 24,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,76; 24,76</t>
+          <t>20,79; 24,6</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 22,36</t>
+          <t>14,41; 22,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,82; 19,29</t>
+          <t>10,65; 18,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 23,5</t>
+          <t>14,09; 23,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 20,09</t>
+          <t>12,45; 20,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 27,09</t>
+          <t>17,28; 26,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 25,66</t>
+          <t>15,09; 26,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,71; 29,56</t>
+          <t>19,14; 29,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 24,18</t>
+          <t>17,58; 24,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 23,0</t>
+          <t>16,98; 22,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,55; 20,27</t>
+          <t>13,77; 20,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,56; 24,33</t>
+          <t>17,81; 24,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 20,85</t>
+          <t>15,94; 21,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,95; 26,94</t>
+          <t>22,72; 26,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,13; 25,7</t>
+          <t>21,12; 25,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,49; 27,21</t>
+          <t>22,43; 27,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 20,87</t>
+          <t>18,2; 22,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,23; 24,23</t>
+          <t>18,7; 24,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 26,07</t>
+          <t>20,1; 25,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 23,52</t>
+          <t>18,67; 23,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 30,08</t>
+          <t>21,27; 24,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 25,42</t>
+          <t>22,24; 25,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,61; 25,02</t>
+          <t>21,47; 24,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,61; 25,02</t>
+          <t>21,38; 24,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 23,38</t>
+          <t>20,02; 22,9</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54200</t>
+          <t>60722</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93924; 130014</t>
+          <t>94423; 131113</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45725; 71693</t>
+          <t>45951; 71288</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44353; 68077</t>
+          <t>43834; 67517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20530; 39937</t>
+          <t>26280; 48331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27814; 51069</t>
+          <t>28101; 49489</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27454; 49099</t>
+          <t>28793; 50045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11107; 26400</t>
+          <t>11882; 26938</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17980; 38843</t>
+          <t>17378; 31693</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126307; 169820</t>
+          <t>128107; 170282</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81889; 114424</t>
+          <t>80163; 114480</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59771; 87669</t>
+          <t>59384; 87608</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41372; 68713</t>
+          <t>48202; 76032</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>239580</t>
+          <t>269736</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>238368</t>
+          <t>220862</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>477948</t>
+          <t>490598</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>255359; 316321</t>
+          <t>256680; 319534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>200203; 254018</t>
+          <t>199382; 254359</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204028; 257110</t>
+          <t>202211; 254782</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>141429; 303579</t>
+          <t>237501; 299304</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>99337; 136723</t>
+          <t>99878; 136496</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>113078; 152235</t>
+          <t>109732; 152218</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>103232; 145667</t>
+          <t>106647; 148124</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>184549; 316947</t>
+          <t>196969; 243475</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>373136; 442629</t>
+          <t>372967; 442836</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323724; 392025</t>
+          <t>323461; 392367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>319342; 389475</t>
+          <t>325058; 385244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>337741; 566409</t>
+          <t>452245; 535161</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69526</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90695</t>
+          <t>99411</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>160221</t>
+          <t>177175</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59683; 90633</t>
+          <t>58425; 91018</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34215; 61015</t>
+          <t>33685; 59332</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49208; 81458</t>
+          <t>48854; 79962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55365; 89487</t>
+          <t>60451; 99876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>51497; 78943</t>
+          <t>50347; 78471</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34207; 60274</t>
+          <t>35436; 61814</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60180; 90255</t>
+          <t>58461; 88952</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74494; 105518</t>
+          <t>84244; 115279</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117316; 160206</t>
+          <t>118321; 159068</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74707; 111718</t>
+          <t>75883; 113079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114460; 158635</t>
+          <t>116125; 161608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>139340; 183807</t>
+          <t>153869; 202719</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338320</t>
+          <t>383716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>354049</t>
+          <t>344779</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>692369</t>
+          <t>728496</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>434510; 510003</t>
+          <t>430098; 508849</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>298910; 363615</t>
+          <t>298747; 365684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316405; 382777</t>
+          <t>315597; 382128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>220888; 404307</t>
+          <t>345634; 423244</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>196389; 247541</t>
+          <t>190991; 247029</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>191311; 247103</t>
+          <t>190493; 243195</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>190735; 241835</t>
+          <t>191925; 244831</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>300676; 434694</t>
+          <t>317788; 371579</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>646055; 740870</t>
+          <t>648329; 738299</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>510530; 591191</t>
+          <t>507201; 588626</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>526318; 609260</t>
+          <t>520687; 606464</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>529111; 790612</t>
+          <t>679247; 776903</t>
         </is>
       </c>
     </row>
